--- a/data/in/WeatherData_ThermalLandscapes_curated_v2.xlsx
+++ b/data/in/WeatherData_ThermalLandscapes_curated_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d208f1c5c7e8ef3/Documents/Python/ThermalLandscapes/data/in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{1B6851DE-72A1-4709-B371-AC96BDE2FB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89F734D3-2823-476B-A2B0-994C218B3429}"/>
+  <xr:revisionPtr revIDLastSave="171" documentId="8_{1B6851DE-72A1-4709-B371-AC96BDE2FB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23960422-266B-4019-9D97-18032A391886}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B4E39C6E-1CC0-4BBA-8DDC-D90252A6E433}"/>
   </bookViews>
@@ -592,13 +592,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53C81A0-23E2-4182-88EB-933B19C50330}">
-  <dimension ref="A1:W168"/>
+  <dimension ref="A1:W216"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="22" width="9.140625" customWidth="1"/>
+    <col min="4" max="10" width="9.140625" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="21" width="9.140625" customWidth="1"/>
+    <col min="22" max="22" width="16.7109375" customWidth="1"/>
+    <col min="23" max="24" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
@@ -7372,1704 +7378,1704 @@
       </c>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
+      <c r="A97" t="s">
         <v>25</v>
       </c>
       <c r="B97" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C97" s="10">
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="D97" s="9">
-        <v>18.100000000000001</v>
+        <v>22.39</v>
       </c>
       <c r="E97" s="9">
-        <v>18.100000000000001</v>
+        <v>22.62</v>
       </c>
       <c r="F97" s="9">
-        <v>18.100000000000001</v>
+        <v>22.29</v>
       </c>
       <c r="G97" s="9">
-        <v>97</v>
+        <v>66.5</v>
       </c>
       <c r="H97" s="9">
-        <v>17.62</v>
+        <v>15.85</v>
       </c>
       <c r="I97" s="9">
         <v>0</v>
       </c>
       <c r="J97" s="9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="K97" s="9">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="L97" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M97" s="9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="N97" s="9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="O97" s="9">
         <v>0</v>
       </c>
       <c r="P97" s="9">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q97" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R97" s="9">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="S97" s="9">
-        <v>15.03</v>
+        <v>13.51</v>
       </c>
       <c r="T97" s="9">
-        <v>14.46</v>
+        <v>12.55</v>
       </c>
       <c r="U97" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V97" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W97" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
+      <c r="A98" t="s">
         <v>25</v>
       </c>
       <c r="B98" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C98" s="10">
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="D98" s="9">
-        <v>18.100000000000001</v>
+        <v>22.49</v>
       </c>
       <c r="E98" s="9">
-        <v>18.100000000000001</v>
+        <v>22.68</v>
       </c>
       <c r="F98" s="9">
-        <v>18.100000000000001</v>
+        <v>22.37</v>
       </c>
       <c r="G98" s="9">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="H98" s="9">
-        <v>17.62</v>
+        <v>15.82</v>
       </c>
       <c r="I98" s="9">
         <v>0</v>
       </c>
       <c r="J98" s="9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="K98" s="9">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L98" t="s">
         <v>10</v>
       </c>
       <c r="M98" s="9">
-        <v>1.44</v>
+        <v>0.43</v>
       </c>
       <c r="N98" s="9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="O98" s="9">
         <v>0</v>
       </c>
       <c r="P98" s="9">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q98" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" s="9">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="S98" s="9">
-        <v>15.03</v>
+        <v>13.49</v>
       </c>
       <c r="T98" s="9">
-        <v>14.46</v>
+        <v>12.53</v>
       </c>
       <c r="U98" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V98" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W98" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
+      <c r="A99" t="s">
         <v>25</v>
       </c>
       <c r="B99" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C99" s="10">
         <v>0.125</v>
       </c>
       <c r="D99" s="9">
-        <v>18.3</v>
+        <v>22.67</v>
       </c>
       <c r="E99" s="9">
-        <v>18.3</v>
+        <v>22.79</v>
       </c>
       <c r="F99" s="9">
-        <v>18.3</v>
+        <v>22.46</v>
       </c>
       <c r="G99" s="9">
-        <v>97</v>
+        <v>66.3</v>
       </c>
       <c r="H99" s="9">
-        <v>17.82</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="I99" s="9">
         <v>0</v>
       </c>
       <c r="J99" s="9">
-        <v>2.16</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K99" s="9">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L99" t="s">
         <v>10</v>
       </c>
       <c r="M99" s="9">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="N99" s="9">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O99" s="9">
         <v>0</v>
       </c>
       <c r="P99" s="9">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q99" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" s="9">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="S99" s="9">
-        <v>15.21</v>
+        <v>13.69</v>
       </c>
       <c r="T99" s="9">
-        <v>14.65</v>
+        <v>12.72</v>
       </c>
       <c r="U99" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V99" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W99" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
+      <c r="A100" t="s">
         <v>25</v>
       </c>
       <c r="B100" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C100" s="10">
         <v>0.16666666666666666</v>
       </c>
       <c r="D100" s="9">
-        <v>18.7</v>
+        <v>21.77</v>
       </c>
       <c r="E100" s="9">
-        <v>18.7</v>
+        <v>22.36</v>
       </c>
       <c r="F100" s="9">
-        <v>18.7</v>
+        <v>21.41</v>
       </c>
       <c r="G100" s="9">
-        <v>97</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="H100" s="9">
-        <v>18.21</v>
+        <v>15.81</v>
       </c>
       <c r="I100" s="9">
         <v>0</v>
       </c>
       <c r="J100" s="9">
-        <v>2.88</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K100" s="9">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="L100" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M100" s="9">
-        <v>3.96</v>
+        <v>1.44</v>
       </c>
       <c r="N100" s="9">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O100" s="9">
         <v>0</v>
       </c>
       <c r="P100" s="9">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q100" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R100" s="9">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="S100" s="9">
-        <v>15.58</v>
+        <v>13.48</v>
       </c>
       <c r="T100" s="9">
-        <v>15.02</v>
+        <v>12.51</v>
       </c>
       <c r="U100" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V100" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W100" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
+      <c r="A101" t="s">
         <v>25</v>
       </c>
       <c r="B101" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C101" s="10">
         <v>0.20833333333333334</v>
       </c>
       <c r="D101" s="9">
-        <v>18.8</v>
+        <v>21.07</v>
       </c>
       <c r="E101" s="9">
-        <v>18.8</v>
+        <v>21.3</v>
       </c>
       <c r="F101" s="9">
-        <v>18.8</v>
+        <v>21.04</v>
       </c>
       <c r="G101" s="9">
-        <v>96</v>
+        <v>70.7</v>
       </c>
       <c r="H101" s="9">
-        <v>18.149999999999999</v>
+        <v>15.54</v>
       </c>
       <c r="I101" s="9">
         <v>0</v>
       </c>
       <c r="J101" s="9">
-        <v>2.88</v>
+        <v>0.04</v>
       </c>
       <c r="K101" s="9">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="L101" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M101" s="9">
-        <v>3.96</v>
+        <v>0.79</v>
       </c>
       <c r="N101" s="9">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O101" s="9">
         <v>0</v>
       </c>
       <c r="P101" s="9">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q101" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="S101" s="9">
-        <v>15.52</v>
+        <v>13.27</v>
       </c>
       <c r="T101" s="9">
-        <v>14.96</v>
+        <v>12.29</v>
       </c>
       <c r="U101" s="9">
-        <v>6.9</v>
+        <v>4.09</v>
       </c>
       <c r="V101" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W101" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A102" s="3" t="s">
+      <c r="A102" t="s">
         <v>25</v>
       </c>
       <c r="B102" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C102" s="10">
         <v>0.25</v>
       </c>
       <c r="D102" s="9">
-        <v>19</v>
+        <v>21.64</v>
       </c>
       <c r="E102" s="9">
-        <v>19</v>
+        <v>22.46</v>
       </c>
       <c r="F102" s="9">
-        <v>19</v>
+        <v>21.07</v>
       </c>
       <c r="G102" s="9">
-        <v>93</v>
+        <v>70.2</v>
       </c>
       <c r="H102" s="9">
-        <v>17.84</v>
+        <v>15.98</v>
       </c>
       <c r="I102" s="9">
         <v>0</v>
       </c>
       <c r="J102" s="9">
-        <v>2.16</v>
+        <v>0.32</v>
       </c>
       <c r="K102" s="9">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="L102" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M102" s="9">
-        <v>2.52</v>
+        <v>1.37</v>
       </c>
       <c r="N102" s="9">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O102" s="9">
         <v>0</v>
       </c>
       <c r="P102" s="9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q102" s="9">
         <v>1</v>
       </c>
       <c r="R102" s="9">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="S102" s="9">
-        <v>15.23</v>
+        <v>13.62</v>
       </c>
       <c r="T102" s="9">
-        <v>14.68</v>
+        <v>12.64</v>
       </c>
       <c r="U102" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V102" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W102" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A103" s="3" t="s">
+      <c r="A103" t="s">
         <v>25</v>
       </c>
       <c r="B103" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C103" s="10">
         <v>0.29166666666666669</v>
       </c>
       <c r="D103" s="9">
-        <v>19.600000000000001</v>
+        <v>23.91</v>
       </c>
       <c r="E103" s="9">
-        <v>19.600000000000001</v>
+        <v>24.35</v>
       </c>
       <c r="F103" s="9">
-        <v>19.600000000000001</v>
+        <v>22.81</v>
       </c>
       <c r="G103" s="9">
-        <v>90</v>
+        <v>68.3</v>
       </c>
       <c r="H103" s="9">
-        <v>17.91</v>
+        <v>17.71</v>
       </c>
       <c r="I103" s="9">
         <v>0</v>
       </c>
       <c r="J103" s="9">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="K103" s="9">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L103" t="s">
         <v>13</v>
       </c>
       <c r="M103" s="9">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="N103" s="9">
-        <v>2.16</v>
+        <v>0.61</v>
       </c>
       <c r="O103" s="9">
         <v>0</v>
       </c>
       <c r="P103" s="9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q103" s="9">
         <v>1</v>
       </c>
       <c r="R103" s="9">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="S103" s="9">
-        <v>15.3</v>
+        <v>15.12</v>
       </c>
       <c r="T103" s="9">
-        <v>14.76</v>
+        <v>14.12</v>
       </c>
       <c r="U103" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V103" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W103" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A104" s="3" t="s">
+      <c r="A104" t="s">
         <v>25</v>
       </c>
       <c r="B104" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C104" s="10">
         <v>0.33333333333333331</v>
       </c>
       <c r="D104" s="9">
-        <v>19.399999999999999</v>
+        <v>25.12</v>
       </c>
       <c r="E104" s="9">
-        <v>19.399999999999999</v>
+        <v>25.82</v>
       </c>
       <c r="F104" s="9">
-        <v>19.399999999999999</v>
+        <v>24.38</v>
       </c>
       <c r="G104" s="9">
-        <v>94</v>
+        <v>67.8</v>
       </c>
       <c r="H104" s="9">
-        <v>18.41</v>
+        <v>18.75</v>
       </c>
       <c r="I104" s="9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="9">
-        <v>2.88</v>
+        <v>1.3</v>
       </c>
       <c r="K104" s="9">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="L104" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M104" s="9">
-        <v>3.96</v>
+        <v>3.64</v>
       </c>
       <c r="N104" s="9">
-        <v>2.88</v>
+        <v>0.36</v>
       </c>
       <c r="O104" s="9">
         <v>0</v>
       </c>
       <c r="P104" s="9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q104" s="9">
         <v>1</v>
       </c>
       <c r="R104" s="9">
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="S104" s="9">
-        <v>15.76</v>
+        <v>16.079999999999998</v>
       </c>
       <c r="T104" s="9">
-        <v>15.22</v>
+        <v>15.08</v>
       </c>
       <c r="U104" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V104" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W104" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A105" s="3" t="s">
+      <c r="A105" t="s">
         <v>25</v>
       </c>
       <c r="B105" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C105" s="10">
         <v>0.375</v>
       </c>
       <c r="D105" s="9">
-        <v>20.3</v>
+        <v>28.6</v>
       </c>
       <c r="E105" s="9">
-        <v>20.3</v>
+        <v>29.79</v>
       </c>
       <c r="F105" s="9">
-        <v>20.3</v>
+        <v>26.22</v>
       </c>
       <c r="G105" s="9">
-        <v>92</v>
+        <v>60.3</v>
       </c>
       <c r="H105" s="9">
-        <v>18.96</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="I105" s="9">
         <v>0</v>
       </c>
       <c r="J105" s="9">
-        <v>2.16</v>
+        <v>2.84</v>
       </c>
       <c r="K105" s="9">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="L105" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M105" s="9">
-        <v>2.52</v>
+        <v>4.82</v>
       </c>
       <c r="N105" s="9">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O105" s="9">
         <v>0</v>
       </c>
       <c r="P105" s="9">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q105" s="9">
         <v>1</v>
       </c>
       <c r="R105" s="9">
-        <v>0.06</v>
+        <v>0.72</v>
       </c>
       <c r="S105" s="9">
-        <v>16.28</v>
+        <v>17.46</v>
       </c>
       <c r="T105" s="9">
-        <v>15.76</v>
+        <v>16.54</v>
       </c>
       <c r="U105" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V105" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W105" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A106" s="3" t="s">
+      <c r="A106" t="s">
         <v>25</v>
       </c>
       <c r="B106" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C106" s="10">
         <v>0.41666666666666669</v>
       </c>
       <c r="D106" s="9">
-        <v>26.2</v>
+        <v>30.86</v>
       </c>
       <c r="E106" s="9">
-        <v>26.2</v>
+        <v>31.59</v>
       </c>
       <c r="F106" s="9">
-        <v>26.2</v>
+        <v>29.84</v>
       </c>
       <c r="G106" s="9">
-        <v>65</v>
+        <v>52.9</v>
       </c>
       <c r="H106" s="9">
-        <v>19.100000000000001</v>
+        <v>20.13</v>
       </c>
       <c r="I106" s="9">
         <v>0</v>
       </c>
       <c r="J106" s="9">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="K106" s="9">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="L106" t="s">
         <v>17</v>
       </c>
       <c r="M106" s="9">
-        <v>3.96</v>
+        <v>7.56</v>
       </c>
       <c r="N106" s="9">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="O106" s="9">
         <v>0</v>
       </c>
       <c r="P106" s="9">
-        <v>1.5</v>
+        <v>3.61</v>
       </c>
       <c r="Q106" s="9">
         <v>1</v>
       </c>
       <c r="R106" s="9">
-        <v>0.28999999999999998</v>
+        <v>0.75</v>
       </c>
       <c r="S106" s="9">
-        <v>16.41</v>
+        <v>17.440000000000001</v>
       </c>
       <c r="T106" s="9">
-        <v>16.05</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="U106" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V106" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W106" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A107" s="3" t="s">
+      <c r="A107" t="s">
         <v>25</v>
       </c>
       <c r="B107" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C107" s="10">
         <v>0.45833333333333331</v>
       </c>
       <c r="D107" s="9">
-        <v>28.7</v>
+        <v>31.34</v>
       </c>
       <c r="E107" s="9">
-        <v>28.7</v>
+        <v>31.98</v>
       </c>
       <c r="F107" s="9">
-        <v>28.7</v>
+        <v>30.9</v>
       </c>
       <c r="G107" s="9">
-        <v>57</v>
+        <v>51.2</v>
       </c>
       <c r="H107" s="9">
-        <v>19.34</v>
+        <v>20.05</v>
       </c>
       <c r="I107" s="9">
         <v>0</v>
       </c>
       <c r="J107" s="9">
-        <v>3.96</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="K107" s="9">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L107" t="s">
         <v>17</v>
       </c>
       <c r="M107" s="9">
-        <v>5.4</v>
+        <v>6.73</v>
       </c>
       <c r="N107" s="9">
-        <v>3.96</v>
+        <v>2.92</v>
       </c>
       <c r="O107" s="9">
         <v>0</v>
       </c>
       <c r="P107" s="9">
-        <v>2</v>
+        <v>3.62</v>
       </c>
       <c r="Q107" s="9">
         <v>1</v>
       </c>
       <c r="R107" s="9">
-        <v>0.41</v>
+        <v>0.76</v>
       </c>
       <c r="S107" s="9">
-        <v>16.64</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="T107" s="9">
-        <v>16.36</v>
+        <v>16.53</v>
       </c>
       <c r="U107" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V107" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W107" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
+      <c r="A108" t="s">
         <v>25</v>
       </c>
       <c r="B108" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C108" s="10">
         <v>0.5</v>
       </c>
       <c r="D108" s="9">
-        <v>31.1</v>
+        <v>30.57</v>
       </c>
       <c r="E108" s="9">
-        <v>31.1</v>
+        <v>31.86</v>
       </c>
       <c r="F108" s="9">
-        <v>31.1</v>
+        <v>30.12</v>
       </c>
       <c r="G108" s="9">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H108" s="9">
-        <v>20.079999999999998</v>
+        <v>19.28</v>
       </c>
       <c r="I108" s="9">
         <v>0</v>
       </c>
       <c r="J108" s="9">
-        <v>3.96</v>
+        <v>4.18</v>
       </c>
       <c r="K108" s="9">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L108" t="s">
         <v>17</v>
       </c>
       <c r="M108" s="9">
-        <v>5.4</v>
+        <v>6.19</v>
       </c>
       <c r="N108" s="9">
-        <v>3.96</v>
+        <v>3.2</v>
       </c>
       <c r="O108" s="9">
         <v>0</v>
       </c>
       <c r="P108" s="9">
-        <v>2.2999999999999998</v>
+        <v>3.62</v>
       </c>
       <c r="Q108" s="9">
         <v>1</v>
       </c>
       <c r="R108" s="9">
-        <v>0.49</v>
+        <v>0.75</v>
       </c>
       <c r="S108" s="9">
-        <v>17.38</v>
+        <v>16.59</v>
       </c>
       <c r="T108" s="9">
-        <v>17.21</v>
+        <v>15.74</v>
       </c>
       <c r="U108" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V108" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W108" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A109" s="3" t="s">
+      <c r="A109" t="s">
         <v>25</v>
       </c>
       <c r="B109" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C109" s="10">
         <v>0.54166666666666663</v>
       </c>
       <c r="D109" s="9">
-        <v>31.1</v>
+        <v>31.68</v>
       </c>
       <c r="E109" s="9">
-        <v>31.1</v>
+        <v>32.01</v>
       </c>
       <c r="F109" s="9">
-        <v>31.1</v>
+        <v>30.92</v>
       </c>
       <c r="G109" s="9">
-        <v>52</v>
+        <v>46.6</v>
       </c>
       <c r="H109" s="9">
-        <v>20.079999999999998</v>
+        <v>18.84</v>
       </c>
       <c r="I109" s="9">
         <v>0</v>
       </c>
       <c r="J109" s="9">
-        <v>6.84</v>
+        <v>3.56</v>
       </c>
       <c r="K109" s="9">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="L109" t="s">
         <v>20</v>
       </c>
       <c r="M109" s="9">
-        <v>9.36</v>
+        <v>6.19</v>
       </c>
       <c r="N109" s="9">
-        <v>6.84</v>
+        <v>2.77</v>
       </c>
       <c r="O109" s="9">
         <v>0</v>
       </c>
       <c r="P109" s="9">
-        <v>2.5</v>
+        <v>3.62</v>
       </c>
       <c r="Q109" s="9">
         <v>1</v>
       </c>
       <c r="R109" s="9">
-        <v>0.54</v>
+        <v>0.76</v>
       </c>
       <c r="S109" s="9">
-        <v>17.38</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="T109" s="9">
-        <v>17.21</v>
+        <v>15.36</v>
       </c>
       <c r="U109" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V109" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W109" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A110" s="3" t="s">
+      <c r="A110" t="s">
         <v>25</v>
       </c>
       <c r="B110" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C110" s="10">
         <v>0.58333333333333337</v>
       </c>
       <c r="D110" s="9">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="E110" s="9">
-        <v>30.1</v>
+        <v>31.7</v>
       </c>
       <c r="F110" s="9">
-        <v>30.1</v>
+        <v>30.22</v>
       </c>
       <c r="G110" s="9">
-        <v>53</v>
+        <v>52.1</v>
       </c>
       <c r="H110" s="9">
-        <v>19.46</v>
+        <v>19.649999999999999</v>
       </c>
       <c r="I110" s="9">
         <v>0</v>
       </c>
       <c r="J110" s="9">
-        <v>6.12</v>
+        <v>4.54</v>
       </c>
       <c r="K110" s="9">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="L110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M110" s="9">
         <v>7.92</v>
       </c>
       <c r="N110" s="9">
-        <v>6.12</v>
+        <v>3.56</v>
       </c>
       <c r="O110" s="9">
         <v>0</v>
       </c>
       <c r="P110" s="9">
-        <v>2.2999999999999998</v>
+        <v>3.62</v>
       </c>
       <c r="Q110" s="9">
         <v>1</v>
       </c>
       <c r="R110" s="9">
-        <v>0.49</v>
+        <v>0.75</v>
       </c>
       <c r="S110" s="9">
-        <v>16.77</v>
+        <v>16.95</v>
       </c>
       <c r="T110" s="9">
-        <v>16.54</v>
+        <v>16.11</v>
       </c>
       <c r="U110" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V110" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W110" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A111" s="3" t="s">
+      <c r="A111" t="s">
         <v>25</v>
       </c>
       <c r="B111" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C111" s="10">
         <v>0.625</v>
       </c>
       <c r="D111" s="9">
-        <v>28.7</v>
+        <v>30.82</v>
       </c>
       <c r="E111" s="9">
-        <v>28.7</v>
+        <v>31.81</v>
       </c>
       <c r="F111" s="9">
-        <v>28.7</v>
+        <v>29.92</v>
       </c>
       <c r="G111" s="9">
-        <v>59</v>
+        <v>54.1</v>
       </c>
       <c r="H111" s="9">
-        <v>19.89</v>
+        <v>20.46</v>
       </c>
       <c r="I111" s="9">
         <v>0</v>
       </c>
       <c r="J111" s="9">
-        <v>9</v>
+        <v>5.18</v>
       </c>
       <c r="K111" s="9">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="L111" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M111" s="9">
-        <v>11.88</v>
+        <v>7.56</v>
       </c>
       <c r="N111" s="9">
-        <v>9</v>
+        <v>4.72</v>
       </c>
       <c r="O111" s="9">
         <v>0</v>
       </c>
       <c r="P111" s="9">
-        <v>1.3</v>
+        <v>3.61</v>
       </c>
       <c r="Q111" s="9">
         <v>1</v>
       </c>
       <c r="R111" s="9">
-        <v>0.31</v>
+        <v>0.75</v>
       </c>
       <c r="S111" s="9">
-        <v>17.2</v>
+        <v>17.78</v>
       </c>
       <c r="T111" s="9">
-        <v>16.93</v>
+        <v>16.940000000000001</v>
       </c>
       <c r="U111" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V111" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W111" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A112" s="3" t="s">
+      <c r="A112" t="s">
         <v>25</v>
       </c>
       <c r="B112" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C112" s="10">
         <v>0.66666666666666663</v>
       </c>
       <c r="D112" s="9">
-        <v>28.1</v>
+        <v>30.02</v>
       </c>
       <c r="E112" s="9">
-        <v>28.1</v>
+        <v>30.86</v>
       </c>
       <c r="F112" s="9">
-        <v>28.1</v>
+        <v>29.58</v>
       </c>
       <c r="G112" s="9">
-        <v>63</v>
+        <v>54.3</v>
       </c>
       <c r="H112" s="9">
-        <v>20.39</v>
+        <v>19.78</v>
       </c>
       <c r="I112" s="9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J112" s="9">
-        <v>6.12</v>
+        <v>5</v>
       </c>
       <c r="K112" s="9">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L112" t="s">
         <v>20</v>
       </c>
       <c r="M112" s="9">
-        <v>7.92</v>
+        <v>7.74</v>
       </c>
       <c r="N112" s="9">
-        <v>6.12</v>
+        <v>4.18</v>
       </c>
       <c r="O112" s="9">
         <v>0</v>
       </c>
       <c r="P112" s="9">
-        <v>1.2</v>
+        <v>3.62</v>
       </c>
       <c r="Q112" s="9">
         <v>1</v>
       </c>
       <c r="R112" s="9">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="S112" s="9">
-        <v>17.71</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="T112" s="9">
-        <v>17.440000000000001</v>
+        <v>16.22</v>
       </c>
       <c r="U112" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V112" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W112" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A113" s="3" t="s">
+      <c r="A113" t="s">
         <v>25</v>
       </c>
       <c r="B113" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C113" s="10">
         <v>0.70833333333333337</v>
       </c>
       <c r="D113" s="9">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="E113" s="9">
-        <v>29.2</v>
+        <v>29.5</v>
       </c>
       <c r="F113" s="9">
-        <v>29.2</v>
+        <v>28.68</v>
       </c>
       <c r="G113" s="9">
+        <v>56.7</v>
+      </c>
+      <c r="H113" s="9">
+        <v>19.62</v>
+      </c>
+      <c r="I113" s="9">
+        <v>0</v>
+      </c>
+      <c r="J113" s="9">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K113" s="9">
         <v>61</v>
       </c>
-      <c r="H113" s="9">
-        <v>20.9</v>
-      </c>
-      <c r="I113" s="9">
-        <v>0</v>
-      </c>
-      <c r="J113" s="9">
-        <v>9</v>
-      </c>
-      <c r="K113" s="9">
-        <v>90</v>
-      </c>
       <c r="L113" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M113" s="9">
-        <v>11.88</v>
+        <v>6.88</v>
       </c>
       <c r="N113" s="9">
-        <v>9</v>
+        <v>3.89</v>
       </c>
       <c r="O113" s="9">
         <v>0</v>
       </c>
       <c r="P113" s="9">
-        <v>2.2000000000000002</v>
+        <v>3.61</v>
       </c>
       <c r="Q113" s="9">
         <v>1</v>
       </c>
       <c r="R113" s="9">
-        <v>0.45</v>
+        <v>0.72</v>
       </c>
       <c r="S113" s="9">
-        <v>18.239999999999998</v>
+        <v>16.93</v>
       </c>
       <c r="T113" s="9">
-        <v>18.04</v>
+        <v>16.03</v>
       </c>
       <c r="U113" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V113" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W113" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A114" s="3" t="s">
+      <c r="A114" t="s">
         <v>25</v>
       </c>
       <c r="B114" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C114" s="10">
         <v>0.75</v>
       </c>
       <c r="D114" s="9">
-        <v>26</v>
+        <v>28.2</v>
       </c>
       <c r="E114" s="9">
-        <v>26</v>
+        <v>28.63</v>
       </c>
       <c r="F114" s="9">
-        <v>26</v>
+        <v>27.89</v>
       </c>
       <c r="G114" s="9">
-        <v>71</v>
+        <v>57.6</v>
       </c>
       <c r="H114" s="9">
-        <v>20.329999999999998</v>
+        <v>19.04</v>
       </c>
       <c r="I114" s="9">
         <v>0</v>
       </c>
       <c r="J114" s="9">
-        <v>5.04</v>
+        <v>4.54</v>
       </c>
       <c r="K114" s="9">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L114" t="s">
         <v>20</v>
       </c>
       <c r="M114" s="9">
-        <v>6.84</v>
+        <v>7.24</v>
       </c>
       <c r="N114" s="9">
-        <v>5.04</v>
+        <v>3.67</v>
       </c>
       <c r="O114" s="9">
         <v>0</v>
       </c>
       <c r="P114" s="9">
-        <v>0.9</v>
+        <v>3.61</v>
       </c>
       <c r="Q114" s="9">
         <v>1</v>
       </c>
       <c r="R114" s="9">
-        <v>0.16</v>
+        <v>0.71</v>
       </c>
       <c r="S114" s="9">
-        <v>17.64</v>
+        <v>16.36</v>
       </c>
       <c r="T114" s="9">
-        <v>17.309999999999999</v>
+        <v>15.44</v>
       </c>
       <c r="U114" s="9">
-        <v>6.9</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="V114" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W114" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A115" s="3" t="s">
+      <c r="A115" t="s">
         <v>25</v>
       </c>
       <c r="B115" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C115" s="10">
         <v>0.79166666666666663</v>
       </c>
       <c r="D115" s="9">
-        <v>24.4</v>
+        <v>27.54</v>
       </c>
       <c r="E115" s="9">
-        <v>24.4</v>
+        <v>27.88</v>
       </c>
       <c r="F115" s="9">
-        <v>24.4</v>
+        <v>27.35</v>
       </c>
       <c r="G115" s="9">
-        <v>79</v>
+        <v>59.6</v>
       </c>
       <c r="H115" s="9">
-        <v>20.52</v>
+        <v>18.97</v>
       </c>
       <c r="I115" s="9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J115" s="9">
-        <v>5.04</v>
+        <v>4.28</v>
       </c>
       <c r="K115" s="9">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="L115" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M115" s="9">
-        <v>6.84</v>
+        <v>6.34</v>
       </c>
       <c r="N115" s="9">
-        <v>5.04</v>
+        <v>3.17</v>
       </c>
       <c r="O115" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P115" s="9">
-        <v>0.7</v>
+        <v>3.61</v>
       </c>
       <c r="Q115" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R115" s="9">
-        <v>0.11</v>
+        <v>0.71</v>
       </c>
       <c r="S115" s="9">
-        <v>17.84</v>
+        <v>16.29</v>
       </c>
       <c r="T115" s="9">
-        <v>17.46</v>
+        <v>15.35</v>
       </c>
       <c r="U115" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V115" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W115" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A116" s="3" t="s">
+      <c r="A116" t="s">
         <v>25</v>
       </c>
       <c r="B116" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C116" s="10">
         <v>0.83333333333333337</v>
       </c>
       <c r="D116" s="9">
-        <v>22.9</v>
+        <v>26.79</v>
       </c>
       <c r="E116" s="9">
-        <v>22.9</v>
+        <v>27.27</v>
       </c>
       <c r="F116" s="9">
-        <v>22.9</v>
+        <v>26.38</v>
       </c>
       <c r="G116" s="9">
-        <v>87</v>
+        <v>63.1</v>
       </c>
       <c r="H116" s="9">
-        <v>20.62</v>
+        <v>19.18</v>
       </c>
       <c r="I116" s="9">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J116" s="9">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="K116" s="9">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="L116" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M116" s="9">
-        <v>5.4</v>
+        <v>5.72</v>
       </c>
       <c r="N116" s="9">
-        <v>3.96</v>
+        <v>3.1</v>
       </c>
       <c r="O116" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P116" s="9">
-        <v>0.6</v>
+        <v>3.61</v>
       </c>
       <c r="Q116" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="S116" s="9">
-        <v>17.940000000000001</v>
+        <v>16.489999999999998</v>
       </c>
       <c r="T116" s="9">
-        <v>17.53</v>
+        <v>15.53</v>
       </c>
       <c r="U116" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V116" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W116" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A117" s="3" t="s">
+      <c r="A117" t="s">
         <v>25</v>
       </c>
       <c r="B117" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C117" s="10">
         <v>0.875</v>
       </c>
       <c r="D117" s="9">
-        <v>22.1</v>
+        <v>25.95</v>
       </c>
       <c r="E117" s="9">
-        <v>22.1</v>
+        <v>26.31</v>
       </c>
       <c r="F117" s="9">
-        <v>22.1</v>
+        <v>25.7</v>
       </c>
       <c r="G117" s="9">
-        <v>91</v>
+        <v>63.6</v>
       </c>
       <c r="H117" s="9">
-        <v>20.56</v>
+        <v>18.510000000000002</v>
       </c>
       <c r="I117" s="9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J117" s="9">
-        <v>5.04</v>
+        <v>1.94</v>
       </c>
       <c r="K117" s="9">
-        <v>135</v>
+        <v>31</v>
       </c>
       <c r="L117" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="M117" s="9">
-        <v>6.84</v>
+        <v>3.53</v>
       </c>
       <c r="N117" s="9">
-        <v>5.04</v>
+        <v>0.86</v>
       </c>
       <c r="O117" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P117" s="9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q117" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" s="9">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="S117" s="9">
-        <v>17.88</v>
+        <v>15.85</v>
       </c>
       <c r="T117" s="9">
-        <v>17.440000000000001</v>
+        <v>14.88</v>
       </c>
       <c r="U117" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V117" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W117" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A118" s="3" t="s">
+      <c r="A118" t="s">
         <v>25</v>
       </c>
       <c r="B118" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C118" s="10">
         <v>0.91666666666666663</v>
       </c>
       <c r="D118" s="9">
-        <v>20.9</v>
+        <v>25.45</v>
       </c>
       <c r="E118" s="9">
-        <v>20.9</v>
+        <v>25.66</v>
       </c>
       <c r="F118" s="9">
-        <v>20.9</v>
+        <v>25.31</v>
       </c>
       <c r="G118" s="9">
-        <v>94</v>
+        <v>65.400000000000006</v>
       </c>
       <c r="H118" s="9">
-        <v>19.899999999999999</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="I118" s="9">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J118" s="9">
-        <v>5.04</v>
+        <v>1.91</v>
       </c>
       <c r="K118" s="9">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="L118" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M118" s="9">
-        <v>6.84</v>
+        <v>3.74</v>
       </c>
       <c r="N118" s="9">
-        <v>5.04</v>
+        <v>1.01</v>
       </c>
       <c r="O118" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P118" s="9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q118" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R118" s="9">
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="S118" s="9">
-        <v>17.2</v>
+        <v>15.83</v>
       </c>
       <c r="T118" s="9">
-        <v>16.71</v>
+        <v>14.85</v>
       </c>
       <c r="U118" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V118" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W118" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A119" s="3" t="s">
+      <c r="A119" t="s">
         <v>25</v>
       </c>
       <c r="B119" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C119" s="10">
         <v>0.95833333333333337</v>
       </c>
       <c r="D119" s="9">
-        <v>20.3</v>
+        <v>25.08</v>
       </c>
       <c r="E119" s="9">
-        <v>20.3</v>
+        <v>25.29</v>
       </c>
       <c r="F119" s="9">
-        <v>20.3</v>
+        <v>24.94</v>
       </c>
       <c r="G119" s="9">
-        <v>95</v>
+        <v>67.2</v>
       </c>
       <c r="H119" s="9">
-        <v>19.47</v>
+        <v>18.57</v>
       </c>
       <c r="I119" s="9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J119" s="9">
-        <v>5.04</v>
+        <v>1.51</v>
       </c>
       <c r="K119" s="9">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="L119" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M119" s="9">
-        <v>6.84</v>
+        <v>3.64</v>
       </c>
       <c r="N119" s="9">
-        <v>5.04</v>
+        <v>0.11</v>
       </c>
       <c r="O119" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P119" s="9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q119" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" s="9">
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="S119" s="9">
-        <v>16.78</v>
+        <v>15.91</v>
       </c>
       <c r="T119" s="9">
-        <v>16.27</v>
+        <v>14.91</v>
       </c>
       <c r="U119" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V119" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W119" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A120" s="3" t="s">
+      <c r="A120" t="s">
         <v>25</v>
       </c>
       <c r="B120" s="8">
-        <v>43853</v>
+        <v>44169</v>
       </c>
       <c r="C120" s="10">
         <v>1</v>
       </c>
       <c r="D120" s="9">
-        <v>19.899999999999999</v>
+        <v>24.71</v>
       </c>
       <c r="E120" s="9">
-        <v>19.899999999999999</v>
+        <v>24.71</v>
       </c>
       <c r="F120" s="9">
-        <v>19.899999999999999</v>
+        <v>24.71</v>
       </c>
       <c r="G120" s="9">
-        <v>97</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="H120" s="9">
-        <v>19.41</v>
+        <v>18.89</v>
       </c>
       <c r="I120" s="9">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="9">
-        <v>3.96</v>
+        <v>0.94</v>
       </c>
       <c r="K120" s="9">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="L120" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M120" s="9">
-        <v>5.4</v>
+        <v>4.07</v>
       </c>
       <c r="N120" s="9">
-        <v>3.96</v>
+        <v>0.94</v>
       </c>
       <c r="O120" s="9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P120" s="9">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q120" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" s="9">
-        <v>0</v>
+        <v>0.69</v>
       </c>
       <c r="S120" s="9">
-        <v>16.72</v>
+        <v>16.21</v>
       </c>
       <c r="T120" s="9">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="U120" s="9">
-        <v>6.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V120" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="W120" t="s">
         <v>31</v>
@@ -12482,6 +12488,966 @@
       <c r="W168" t="s">
         <v>29</v>
       </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B169" s="8"/>
+      <c r="D169" s="9"/>
+      <c r="E169" s="9"/>
+      <c r="F169" s="9"/>
+      <c r="G169" s="9"/>
+      <c r="H169" s="9"/>
+      <c r="I169" s="9"/>
+      <c r="J169" s="9"/>
+      <c r="K169" s="9"/>
+      <c r="M169" s="9"/>
+      <c r="N169" s="9"/>
+      <c r="O169" s="9"/>
+      <c r="P169" s="9"/>
+      <c r="Q169" s="9"/>
+      <c r="R169" s="9"/>
+      <c r="S169" s="9"/>
+      <c r="T169" s="9"/>
+      <c r="U169" s="9"/>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B170" s="8"/>
+      <c r="D170" s="9"/>
+      <c r="E170" s="9"/>
+      <c r="F170" s="9"/>
+      <c r="G170" s="9"/>
+      <c r="H170" s="9"/>
+      <c r="I170" s="9"/>
+      <c r="J170" s="9"/>
+      <c r="K170" s="9"/>
+      <c r="M170" s="9"/>
+      <c r="N170" s="9"/>
+      <c r="O170" s="9"/>
+      <c r="P170" s="9"/>
+      <c r="Q170" s="9"/>
+      <c r="R170" s="9"/>
+      <c r="S170" s="9"/>
+      <c r="T170" s="9"/>
+      <c r="U170" s="9"/>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B171" s="8"/>
+      <c r="D171" s="9"/>
+      <c r="E171" s="9"/>
+      <c r="F171" s="9"/>
+      <c r="G171" s="9"/>
+      <c r="H171" s="9"/>
+      <c r="I171" s="9"/>
+      <c r="J171" s="9"/>
+      <c r="K171" s="9"/>
+      <c r="M171" s="9"/>
+      <c r="N171" s="9"/>
+      <c r="O171" s="9"/>
+      <c r="P171" s="9"/>
+      <c r="Q171" s="9"/>
+      <c r="R171" s="9"/>
+      <c r="S171" s="9"/>
+      <c r="T171" s="9"/>
+      <c r="U171" s="9"/>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B172" s="8"/>
+      <c r="D172" s="9"/>
+      <c r="E172" s="9"/>
+      <c r="F172" s="9"/>
+      <c r="G172" s="9"/>
+      <c r="H172" s="9"/>
+      <c r="I172" s="9"/>
+      <c r="J172" s="9"/>
+      <c r="K172" s="9"/>
+      <c r="M172" s="9"/>
+      <c r="N172" s="9"/>
+      <c r="O172" s="9"/>
+      <c r="P172" s="9"/>
+      <c r="Q172" s="9"/>
+      <c r="R172" s="9"/>
+      <c r="S172" s="9"/>
+      <c r="T172" s="9"/>
+      <c r="U172" s="9"/>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B173" s="8"/>
+      <c r="D173" s="9"/>
+      <c r="E173" s="9"/>
+      <c r="F173" s="9"/>
+      <c r="G173" s="9"/>
+      <c r="H173" s="9"/>
+      <c r="I173" s="9"/>
+      <c r="J173" s="9"/>
+      <c r="K173" s="9"/>
+      <c r="M173" s="9"/>
+      <c r="N173" s="9"/>
+      <c r="O173" s="9"/>
+      <c r="P173" s="9"/>
+      <c r="Q173" s="9"/>
+      <c r="R173" s="9"/>
+      <c r="S173" s="9"/>
+      <c r="T173" s="9"/>
+      <c r="U173" s="9"/>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B174" s="8"/>
+      <c r="D174" s="9"/>
+      <c r="E174" s="9"/>
+      <c r="F174" s="9"/>
+      <c r="G174" s="9"/>
+      <c r="H174" s="9"/>
+      <c r="I174" s="9"/>
+      <c r="J174" s="9"/>
+      <c r="K174" s="9"/>
+      <c r="M174" s="9"/>
+      <c r="N174" s="9"/>
+      <c r="O174" s="9"/>
+      <c r="P174" s="9"/>
+      <c r="Q174" s="9"/>
+      <c r="R174" s="9"/>
+      <c r="S174" s="9"/>
+      <c r="T174" s="9"/>
+      <c r="U174" s="9"/>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B175" s="8"/>
+      <c r="D175" s="9"/>
+      <c r="E175" s="9"/>
+      <c r="F175" s="9"/>
+      <c r="G175" s="9"/>
+      <c r="H175" s="9"/>
+      <c r="I175" s="9"/>
+      <c r="J175" s="9"/>
+      <c r="K175" s="9"/>
+      <c r="M175" s="9"/>
+      <c r="N175" s="9"/>
+      <c r="O175" s="9"/>
+      <c r="P175" s="9"/>
+      <c r="Q175" s="9"/>
+      <c r="R175" s="9"/>
+      <c r="S175" s="9"/>
+      <c r="T175" s="9"/>
+      <c r="U175" s="9"/>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B176" s="8"/>
+      <c r="D176" s="9"/>
+      <c r="E176" s="9"/>
+      <c r="F176" s="9"/>
+      <c r="G176" s="9"/>
+      <c r="H176" s="9"/>
+      <c r="I176" s="9"/>
+      <c r="J176" s="9"/>
+      <c r="K176" s="9"/>
+      <c r="M176" s="9"/>
+      <c r="N176" s="9"/>
+      <c r="O176" s="9"/>
+      <c r="P176" s="9"/>
+      <c r="Q176" s="9"/>
+      <c r="R176" s="9"/>
+      <c r="S176" s="9"/>
+      <c r="T176" s="9"/>
+      <c r="U176" s="9"/>
+    </row>
+    <row r="177" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B177" s="8"/>
+      <c r="D177" s="9"/>
+      <c r="E177" s="9"/>
+      <c r="F177" s="9"/>
+      <c r="G177" s="9"/>
+      <c r="H177" s="9"/>
+      <c r="I177" s="9"/>
+      <c r="J177" s="9"/>
+      <c r="K177" s="9"/>
+      <c r="M177" s="9"/>
+      <c r="N177" s="9"/>
+      <c r="O177" s="9"/>
+      <c r="P177" s="9"/>
+      <c r="Q177" s="9"/>
+      <c r="R177" s="9"/>
+      <c r="S177" s="9"/>
+      <c r="T177" s="9"/>
+      <c r="U177" s="9"/>
+    </row>
+    <row r="178" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B178" s="8"/>
+      <c r="D178" s="9"/>
+      <c r="E178" s="9"/>
+      <c r="F178" s="9"/>
+      <c r="G178" s="9"/>
+      <c r="H178" s="9"/>
+      <c r="I178" s="9"/>
+      <c r="J178" s="9"/>
+      <c r="K178" s="9"/>
+      <c r="M178" s="9"/>
+      <c r="N178" s="9"/>
+      <c r="O178" s="9"/>
+      <c r="P178" s="9"/>
+      <c r="Q178" s="9"/>
+      <c r="R178" s="9"/>
+      <c r="S178" s="9"/>
+      <c r="T178" s="9"/>
+      <c r="U178" s="9"/>
+    </row>
+    <row r="179" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B179" s="8"/>
+      <c r="D179" s="9"/>
+      <c r="E179" s="9"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="9"/>
+      <c r="H179" s="9"/>
+      <c r="I179" s="9"/>
+      <c r="J179" s="9"/>
+      <c r="K179" s="9"/>
+      <c r="M179" s="9"/>
+      <c r="N179" s="9"/>
+      <c r="O179" s="9"/>
+      <c r="P179" s="9"/>
+      <c r="Q179" s="9"/>
+      <c r="R179" s="9"/>
+      <c r="S179" s="9"/>
+      <c r="T179" s="9"/>
+      <c r="U179" s="9"/>
+    </row>
+    <row r="180" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B180" s="8"/>
+      <c r="D180" s="9"/>
+      <c r="E180" s="9"/>
+      <c r="F180" s="9"/>
+      <c r="G180" s="9"/>
+      <c r="H180" s="9"/>
+      <c r="I180" s="9"/>
+      <c r="J180" s="9"/>
+      <c r="K180" s="9"/>
+      <c r="M180" s="9"/>
+      <c r="N180" s="9"/>
+      <c r="O180" s="9"/>
+      <c r="P180" s="9"/>
+      <c r="Q180" s="9"/>
+      <c r="R180" s="9"/>
+      <c r="S180" s="9"/>
+      <c r="T180" s="9"/>
+      <c r="U180" s="9"/>
+    </row>
+    <row r="181" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B181" s="8"/>
+      <c r="D181" s="9"/>
+      <c r="E181" s="9"/>
+      <c r="F181" s="9"/>
+      <c r="G181" s="9"/>
+      <c r="H181" s="9"/>
+      <c r="I181" s="9"/>
+      <c r="J181" s="9"/>
+      <c r="K181" s="9"/>
+      <c r="M181" s="9"/>
+      <c r="N181" s="9"/>
+      <c r="O181" s="9"/>
+      <c r="P181" s="9"/>
+      <c r="Q181" s="9"/>
+      <c r="R181" s="9"/>
+      <c r="S181" s="9"/>
+      <c r="T181" s="9"/>
+      <c r="U181" s="9"/>
+    </row>
+    <row r="182" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B182" s="8"/>
+      <c r="D182" s="9"/>
+      <c r="E182" s="9"/>
+      <c r="F182" s="9"/>
+      <c r="G182" s="9"/>
+      <c r="H182" s="9"/>
+      <c r="I182" s="9"/>
+      <c r="J182" s="9"/>
+      <c r="K182" s="9"/>
+      <c r="M182" s="9"/>
+      <c r="N182" s="9"/>
+      <c r="O182" s="9"/>
+      <c r="P182" s="9"/>
+      <c r="Q182" s="9"/>
+      <c r="R182" s="9"/>
+      <c r="S182" s="9"/>
+      <c r="T182" s="9"/>
+      <c r="U182" s="9"/>
+    </row>
+    <row r="183" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B183" s="8"/>
+      <c r="D183" s="9"/>
+      <c r="E183" s="9"/>
+      <c r="F183" s="9"/>
+      <c r="G183" s="9"/>
+      <c r="H183" s="9"/>
+      <c r="I183" s="9"/>
+      <c r="J183" s="9"/>
+      <c r="K183" s="9"/>
+      <c r="M183" s="9"/>
+      <c r="N183" s="9"/>
+      <c r="O183" s="9"/>
+      <c r="P183" s="9"/>
+      <c r="Q183" s="9"/>
+      <c r="R183" s="9"/>
+      <c r="S183" s="9"/>
+      <c r="T183" s="9"/>
+      <c r="U183" s="9"/>
+    </row>
+    <row r="184" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B184" s="8"/>
+      <c r="D184" s="9"/>
+      <c r="E184" s="9"/>
+      <c r="F184" s="9"/>
+      <c r="G184" s="9"/>
+      <c r="H184" s="9"/>
+      <c r="I184" s="9"/>
+      <c r="J184" s="9"/>
+      <c r="K184" s="9"/>
+      <c r="M184" s="9"/>
+      <c r="N184" s="9"/>
+      <c r="O184" s="9"/>
+      <c r="P184" s="9"/>
+      <c r="Q184" s="9"/>
+      <c r="R184" s="9"/>
+      <c r="S184" s="9"/>
+      <c r="T184" s="9"/>
+      <c r="U184" s="9"/>
+    </row>
+    <row r="185" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B185" s="8"/>
+      <c r="D185" s="9"/>
+      <c r="E185" s="9"/>
+      <c r="F185" s="9"/>
+      <c r="G185" s="9"/>
+      <c r="H185" s="9"/>
+      <c r="I185" s="9"/>
+      <c r="J185" s="9"/>
+      <c r="K185" s="9"/>
+      <c r="M185" s="9"/>
+      <c r="N185" s="9"/>
+      <c r="O185" s="9"/>
+      <c r="P185" s="9"/>
+      <c r="Q185" s="9"/>
+      <c r="R185" s="9"/>
+      <c r="S185" s="9"/>
+      <c r="T185" s="9"/>
+      <c r="U185" s="9"/>
+    </row>
+    <row r="186" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B186" s="8"/>
+      <c r="D186" s="9"/>
+      <c r="E186" s="9"/>
+      <c r="F186" s="9"/>
+      <c r="G186" s="9"/>
+      <c r="H186" s="9"/>
+      <c r="I186" s="9"/>
+      <c r="J186" s="9"/>
+      <c r="K186" s="9"/>
+      <c r="M186" s="9"/>
+      <c r="N186" s="9"/>
+      <c r="O186" s="9"/>
+      <c r="P186" s="9"/>
+      <c r="Q186" s="9"/>
+      <c r="R186" s="9"/>
+      <c r="S186" s="9"/>
+      <c r="T186" s="9"/>
+      <c r="U186" s="9"/>
+    </row>
+    <row r="187" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B187" s="8"/>
+      <c r="D187" s="9"/>
+      <c r="E187" s="9"/>
+      <c r="F187" s="9"/>
+      <c r="G187" s="9"/>
+      <c r="H187" s="9"/>
+      <c r="I187" s="9"/>
+      <c r="J187" s="9"/>
+      <c r="K187" s="9"/>
+      <c r="M187" s="9"/>
+      <c r="N187" s="9"/>
+      <c r="O187" s="9"/>
+      <c r="P187" s="9"/>
+      <c r="Q187" s="9"/>
+      <c r="R187" s="9"/>
+      <c r="S187" s="9"/>
+      <c r="T187" s="9"/>
+      <c r="U187" s="9"/>
+    </row>
+    <row r="188" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B188" s="8"/>
+      <c r="D188" s="9"/>
+      <c r="E188" s="9"/>
+      <c r="F188" s="9"/>
+      <c r="G188" s="9"/>
+      <c r="H188" s="9"/>
+      <c r="I188" s="9"/>
+      <c r="J188" s="9"/>
+      <c r="K188" s="9"/>
+      <c r="M188" s="9"/>
+      <c r="N188" s="9"/>
+      <c r="O188" s="9"/>
+      <c r="P188" s="9"/>
+      <c r="Q188" s="9"/>
+      <c r="R188" s="9"/>
+      <c r="S188" s="9"/>
+      <c r="T188" s="9"/>
+      <c r="U188" s="9"/>
+    </row>
+    <row r="189" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B189" s="8"/>
+      <c r="D189" s="9"/>
+      <c r="E189" s="9"/>
+      <c r="F189" s="9"/>
+      <c r="G189" s="9"/>
+      <c r="H189" s="9"/>
+      <c r="I189" s="9"/>
+      <c r="J189" s="9"/>
+      <c r="K189" s="9"/>
+      <c r="M189" s="9"/>
+      <c r="N189" s="9"/>
+      <c r="O189" s="9"/>
+      <c r="P189" s="9"/>
+      <c r="Q189" s="9"/>
+      <c r="R189" s="9"/>
+      <c r="S189" s="9"/>
+      <c r="T189" s="9"/>
+      <c r="U189" s="9"/>
+    </row>
+    <row r="190" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B190" s="8"/>
+      <c r="D190" s="9"/>
+      <c r="E190" s="9"/>
+      <c r="F190" s="9"/>
+      <c r="G190" s="9"/>
+      <c r="H190" s="9"/>
+      <c r="I190" s="9"/>
+      <c r="J190" s="9"/>
+      <c r="K190" s="9"/>
+      <c r="M190" s="9"/>
+      <c r="N190" s="9"/>
+      <c r="O190" s="9"/>
+      <c r="P190" s="9"/>
+      <c r="Q190" s="9"/>
+      <c r="R190" s="9"/>
+      <c r="S190" s="9"/>
+      <c r="T190" s="9"/>
+      <c r="U190" s="9"/>
+    </row>
+    <row r="191" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B191" s="8"/>
+      <c r="D191" s="9"/>
+      <c r="E191" s="9"/>
+      <c r="F191" s="9"/>
+      <c r="G191" s="9"/>
+      <c r="H191" s="9"/>
+      <c r="I191" s="9"/>
+      <c r="J191" s="9"/>
+      <c r="K191" s="9"/>
+      <c r="M191" s="9"/>
+      <c r="N191" s="9"/>
+      <c r="O191" s="9"/>
+      <c r="P191" s="9"/>
+      <c r="Q191" s="9"/>
+      <c r="R191" s="9"/>
+      <c r="S191" s="9"/>
+      <c r="T191" s="9"/>
+      <c r="U191" s="9"/>
+    </row>
+    <row r="192" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B192" s="8"/>
+      <c r="D192" s="9"/>
+      <c r="E192" s="9"/>
+      <c r="F192" s="9"/>
+      <c r="G192" s="9"/>
+      <c r="H192" s="9"/>
+      <c r="I192" s="9"/>
+      <c r="J192" s="9"/>
+      <c r="K192" s="9"/>
+      <c r="M192" s="9"/>
+      <c r="N192" s="9"/>
+      <c r="O192" s="9"/>
+      <c r="P192" s="9"/>
+      <c r="Q192" s="9"/>
+      <c r="R192" s="9"/>
+      <c r="S192" s="9"/>
+      <c r="T192" s="9"/>
+      <c r="U192" s="9"/>
+    </row>
+    <row r="193" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B193" s="8"/>
+      <c r="D193" s="9"/>
+      <c r="E193" s="9"/>
+      <c r="F193" s="9"/>
+      <c r="G193" s="9"/>
+      <c r="H193" s="9"/>
+      <c r="I193" s="9"/>
+      <c r="J193" s="9"/>
+      <c r="K193" s="9"/>
+      <c r="M193" s="9"/>
+      <c r="N193" s="9"/>
+      <c r="O193" s="9"/>
+      <c r="P193" s="9"/>
+      <c r="Q193" s="9"/>
+      <c r="R193" s="9"/>
+      <c r="S193" s="9"/>
+      <c r="T193" s="9"/>
+      <c r="U193" s="9"/>
+    </row>
+    <row r="194" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B194" s="8"/>
+      <c r="D194" s="9"/>
+      <c r="E194" s="9"/>
+      <c r="F194" s="9"/>
+      <c r="G194" s="9"/>
+      <c r="H194" s="9"/>
+      <c r="I194" s="9"/>
+      <c r="J194" s="9"/>
+      <c r="K194" s="9"/>
+      <c r="M194" s="9"/>
+      <c r="N194" s="9"/>
+      <c r="O194" s="9"/>
+      <c r="P194" s="9"/>
+      <c r="Q194" s="9"/>
+      <c r="R194" s="9"/>
+      <c r="S194" s="9"/>
+      <c r="T194" s="9"/>
+      <c r="U194" s="9"/>
+    </row>
+    <row r="195" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B195" s="8"/>
+      <c r="D195" s="9"/>
+      <c r="E195" s="9"/>
+      <c r="F195" s="9"/>
+      <c r="G195" s="9"/>
+      <c r="H195" s="9"/>
+      <c r="I195" s="9"/>
+      <c r="J195" s="9"/>
+      <c r="K195" s="9"/>
+      <c r="M195" s="9"/>
+      <c r="N195" s="9"/>
+      <c r="O195" s="9"/>
+      <c r="P195" s="9"/>
+      <c r="Q195" s="9"/>
+      <c r="R195" s="9"/>
+      <c r="S195" s="9"/>
+      <c r="T195" s="9"/>
+      <c r="U195" s="9"/>
+    </row>
+    <row r="196" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B196" s="8"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="9"/>
+      <c r="H196" s="9"/>
+      <c r="I196" s="9"/>
+      <c r="J196" s="9"/>
+      <c r="K196" s="9"/>
+      <c r="M196" s="9"/>
+      <c r="N196" s="9"/>
+      <c r="O196" s="9"/>
+      <c r="P196" s="9"/>
+      <c r="Q196" s="9"/>
+      <c r="R196" s="9"/>
+      <c r="S196" s="9"/>
+      <c r="T196" s="9"/>
+      <c r="U196" s="9"/>
+    </row>
+    <row r="197" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B197" s="8"/>
+      <c r="D197" s="9"/>
+      <c r="E197" s="9"/>
+      <c r="F197" s="9"/>
+      <c r="G197" s="9"/>
+      <c r="H197" s="9"/>
+      <c r="I197" s="9"/>
+      <c r="J197" s="9"/>
+      <c r="K197" s="9"/>
+      <c r="M197" s="9"/>
+      <c r="N197" s="9"/>
+      <c r="O197" s="9"/>
+      <c r="P197" s="9"/>
+      <c r="Q197" s="9"/>
+      <c r="R197" s="9"/>
+      <c r="S197" s="9"/>
+      <c r="T197" s="9"/>
+      <c r="U197" s="9"/>
+    </row>
+    <row r="198" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B198" s="8"/>
+      <c r="D198" s="9"/>
+      <c r="E198" s="9"/>
+      <c r="F198" s="9"/>
+      <c r="G198" s="9"/>
+      <c r="H198" s="9"/>
+      <c r="I198" s="9"/>
+      <c r="J198" s="9"/>
+      <c r="K198" s="9"/>
+      <c r="M198" s="9"/>
+      <c r="N198" s="9"/>
+      <c r="O198" s="9"/>
+      <c r="P198" s="9"/>
+      <c r="Q198" s="9"/>
+      <c r="R198" s="9"/>
+      <c r="S198" s="9"/>
+      <c r="T198" s="9"/>
+      <c r="U198" s="9"/>
+    </row>
+    <row r="199" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B199" s="8"/>
+      <c r="D199" s="9"/>
+      <c r="E199" s="9"/>
+      <c r="F199" s="9"/>
+      <c r="G199" s="9"/>
+      <c r="H199" s="9"/>
+      <c r="I199" s="9"/>
+      <c r="J199" s="9"/>
+      <c r="K199" s="9"/>
+      <c r="M199" s="9"/>
+      <c r="N199" s="9"/>
+      <c r="O199" s="9"/>
+      <c r="P199" s="9"/>
+      <c r="Q199" s="9"/>
+      <c r="R199" s="9"/>
+      <c r="S199" s="9"/>
+      <c r="T199" s="9"/>
+      <c r="U199" s="9"/>
+    </row>
+    <row r="200" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B200" s="8"/>
+      <c r="D200" s="9"/>
+      <c r="E200" s="9"/>
+      <c r="F200" s="9"/>
+      <c r="G200" s="9"/>
+      <c r="H200" s="9"/>
+      <c r="I200" s="9"/>
+      <c r="J200" s="9"/>
+      <c r="K200" s="9"/>
+      <c r="M200" s="9"/>
+      <c r="N200" s="9"/>
+      <c r="O200" s="9"/>
+      <c r="P200" s="9"/>
+      <c r="Q200" s="9"/>
+      <c r="R200" s="9"/>
+      <c r="S200" s="9"/>
+      <c r="T200" s="9"/>
+      <c r="U200" s="9"/>
+    </row>
+    <row r="201" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B201" s="8"/>
+      <c r="D201" s="9"/>
+      <c r="E201" s="9"/>
+      <c r="F201" s="9"/>
+      <c r="G201" s="9"/>
+      <c r="H201" s="9"/>
+      <c r="I201" s="9"/>
+      <c r="J201" s="9"/>
+      <c r="K201" s="9"/>
+      <c r="M201" s="9"/>
+      <c r="N201" s="9"/>
+      <c r="O201" s="9"/>
+      <c r="P201" s="9"/>
+      <c r="Q201" s="9"/>
+      <c r="R201" s="9"/>
+      <c r="S201" s="9"/>
+      <c r="T201" s="9"/>
+      <c r="U201" s="9"/>
+    </row>
+    <row r="202" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B202" s="8"/>
+      <c r="D202" s="9"/>
+      <c r="E202" s="9"/>
+      <c r="F202" s="9"/>
+      <c r="G202" s="9"/>
+      <c r="H202" s="9"/>
+      <c r="I202" s="9"/>
+      <c r="J202" s="9"/>
+      <c r="K202" s="9"/>
+      <c r="M202" s="9"/>
+      <c r="N202" s="9"/>
+      <c r="O202" s="9"/>
+      <c r="P202" s="9"/>
+      <c r="Q202" s="9"/>
+      <c r="R202" s="9"/>
+      <c r="S202" s="9"/>
+      <c r="T202" s="9"/>
+      <c r="U202" s="9"/>
+    </row>
+    <row r="203" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B203" s="8"/>
+      <c r="D203" s="9"/>
+      <c r="E203" s="9"/>
+      <c r="F203" s="9"/>
+      <c r="G203" s="9"/>
+      <c r="H203" s="9"/>
+      <c r="I203" s="9"/>
+      <c r="J203" s="9"/>
+      <c r="K203" s="9"/>
+      <c r="M203" s="9"/>
+      <c r="N203" s="9"/>
+      <c r="O203" s="9"/>
+      <c r="P203" s="9"/>
+      <c r="Q203" s="9"/>
+      <c r="R203" s="9"/>
+      <c r="S203" s="9"/>
+      <c r="T203" s="9"/>
+      <c r="U203" s="9"/>
+    </row>
+    <row r="204" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B204" s="8"/>
+      <c r="D204" s="9"/>
+      <c r="E204" s="9"/>
+      <c r="F204" s="9"/>
+      <c r="G204" s="9"/>
+      <c r="H204" s="9"/>
+      <c r="I204" s="9"/>
+      <c r="J204" s="9"/>
+      <c r="K204" s="9"/>
+      <c r="M204" s="9"/>
+      <c r="N204" s="9"/>
+      <c r="O204" s="9"/>
+      <c r="P204" s="9"/>
+      <c r="Q204" s="9"/>
+      <c r="R204" s="9"/>
+      <c r="S204" s="9"/>
+      <c r="T204" s="9"/>
+      <c r="U204" s="9"/>
+    </row>
+    <row r="205" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B205" s="8"/>
+      <c r="D205" s="9"/>
+      <c r="E205" s="9"/>
+      <c r="F205" s="9"/>
+      <c r="G205" s="9"/>
+      <c r="H205" s="9"/>
+      <c r="I205" s="9"/>
+      <c r="J205" s="9"/>
+      <c r="K205" s="9"/>
+      <c r="M205" s="9"/>
+      <c r="N205" s="9"/>
+      <c r="O205" s="9"/>
+      <c r="P205" s="9"/>
+      <c r="Q205" s="9"/>
+      <c r="R205" s="9"/>
+      <c r="S205" s="9"/>
+      <c r="T205" s="9"/>
+      <c r="U205" s="9"/>
+    </row>
+    <row r="206" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B206" s="8"/>
+      <c r="D206" s="9"/>
+      <c r="E206" s="9"/>
+      <c r="F206" s="9"/>
+      <c r="G206" s="9"/>
+      <c r="H206" s="9"/>
+      <c r="I206" s="9"/>
+      <c r="J206" s="9"/>
+      <c r="K206" s="9"/>
+      <c r="M206" s="9"/>
+      <c r="N206" s="9"/>
+      <c r="O206" s="9"/>
+      <c r="P206" s="9"/>
+      <c r="Q206" s="9"/>
+      <c r="R206" s="9"/>
+      <c r="S206" s="9"/>
+      <c r="T206" s="9"/>
+      <c r="U206" s="9"/>
+    </row>
+    <row r="207" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B207" s="8"/>
+      <c r="D207" s="9"/>
+      <c r="E207" s="9"/>
+      <c r="F207" s="9"/>
+      <c r="G207" s="9"/>
+      <c r="H207" s="9"/>
+      <c r="I207" s="9"/>
+      <c r="J207" s="9"/>
+      <c r="K207" s="9"/>
+      <c r="M207" s="9"/>
+      <c r="N207" s="9"/>
+      <c r="O207" s="9"/>
+      <c r="P207" s="9"/>
+      <c r="Q207" s="9"/>
+      <c r="R207" s="9"/>
+      <c r="S207" s="9"/>
+      <c r="T207" s="9"/>
+      <c r="U207" s="9"/>
+    </row>
+    <row r="208" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B208" s="8"/>
+      <c r="D208" s="9"/>
+      <c r="E208" s="9"/>
+      <c r="F208" s="9"/>
+      <c r="G208" s="9"/>
+      <c r="H208" s="9"/>
+      <c r="I208" s="9"/>
+      <c r="J208" s="9"/>
+      <c r="K208" s="9"/>
+      <c r="M208" s="9"/>
+      <c r="N208" s="9"/>
+      <c r="O208" s="9"/>
+      <c r="P208" s="9"/>
+      <c r="Q208" s="9"/>
+      <c r="R208" s="9"/>
+      <c r="S208" s="9"/>
+      <c r="T208" s="9"/>
+      <c r="U208" s="9"/>
+    </row>
+    <row r="209" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B209" s="8"/>
+      <c r="D209" s="9"/>
+      <c r="E209" s="9"/>
+      <c r="F209" s="9"/>
+      <c r="G209" s="9"/>
+      <c r="H209" s="9"/>
+      <c r="I209" s="9"/>
+      <c r="J209" s="9"/>
+      <c r="K209" s="9"/>
+      <c r="M209" s="9"/>
+      <c r="N209" s="9"/>
+      <c r="O209" s="9"/>
+      <c r="P209" s="9"/>
+      <c r="Q209" s="9"/>
+      <c r="R209" s="9"/>
+      <c r="S209" s="9"/>
+      <c r="T209" s="9"/>
+      <c r="U209" s="9"/>
+    </row>
+    <row r="210" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B210" s="8"/>
+      <c r="D210" s="9"/>
+      <c r="E210" s="9"/>
+      <c r="F210" s="9"/>
+      <c r="G210" s="9"/>
+      <c r="H210" s="9"/>
+      <c r="I210" s="9"/>
+      <c r="J210" s="9"/>
+      <c r="K210" s="9"/>
+      <c r="M210" s="9"/>
+      <c r="N210" s="9"/>
+      <c r="O210" s="9"/>
+      <c r="P210" s="9"/>
+      <c r="Q210" s="9"/>
+      <c r="R210" s="9"/>
+      <c r="S210" s="9"/>
+      <c r="T210" s="9"/>
+      <c r="U210" s="9"/>
+    </row>
+    <row r="211" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B211" s="8"/>
+      <c r="D211" s="9"/>
+      <c r="E211" s="9"/>
+      <c r="F211" s="9"/>
+      <c r="G211" s="9"/>
+      <c r="H211" s="9"/>
+      <c r="I211" s="9"/>
+      <c r="J211" s="9"/>
+      <c r="K211" s="9"/>
+      <c r="M211" s="9"/>
+      <c r="N211" s="9"/>
+      <c r="O211" s="9"/>
+      <c r="P211" s="9"/>
+      <c r="Q211" s="9"/>
+      <c r="R211" s="9"/>
+      <c r="S211" s="9"/>
+      <c r="T211" s="9"/>
+      <c r="U211" s="9"/>
+    </row>
+    <row r="212" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B212" s="8"/>
+      <c r="D212" s="9"/>
+      <c r="E212" s="9"/>
+      <c r="F212" s="9"/>
+      <c r="G212" s="9"/>
+      <c r="H212" s="9"/>
+      <c r="I212" s="9"/>
+      <c r="J212" s="9"/>
+      <c r="K212" s="9"/>
+      <c r="M212" s="9"/>
+      <c r="N212" s="9"/>
+      <c r="O212" s="9"/>
+      <c r="P212" s="9"/>
+      <c r="Q212" s="9"/>
+      <c r="R212" s="9"/>
+      <c r="S212" s="9"/>
+      <c r="T212" s="9"/>
+      <c r="U212" s="9"/>
+    </row>
+    <row r="213" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B213" s="8"/>
+      <c r="D213" s="9"/>
+      <c r="E213" s="9"/>
+      <c r="F213" s="9"/>
+      <c r="G213" s="9"/>
+      <c r="H213" s="9"/>
+      <c r="I213" s="9"/>
+      <c r="J213" s="9"/>
+      <c r="K213" s="9"/>
+      <c r="M213" s="9"/>
+      <c r="N213" s="9"/>
+      <c r="O213" s="9"/>
+      <c r="P213" s="9"/>
+      <c r="Q213" s="9"/>
+      <c r="R213" s="9"/>
+      <c r="S213" s="9"/>
+      <c r="T213" s="9"/>
+      <c r="U213" s="9"/>
+    </row>
+    <row r="214" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B214" s="8"/>
+      <c r="D214" s="9"/>
+      <c r="E214" s="9"/>
+      <c r="F214" s="9"/>
+      <c r="G214" s="9"/>
+      <c r="H214" s="9"/>
+      <c r="I214" s="9"/>
+      <c r="J214" s="9"/>
+      <c r="K214" s="9"/>
+      <c r="M214" s="9"/>
+      <c r="N214" s="9"/>
+      <c r="O214" s="9"/>
+      <c r="P214" s="9"/>
+      <c r="Q214" s="9"/>
+      <c r="R214" s="9"/>
+      <c r="S214" s="9"/>
+      <c r="T214" s="9"/>
+      <c r="U214" s="9"/>
+    </row>
+    <row r="215" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B215" s="8"/>
+      <c r="D215" s="9"/>
+      <c r="E215" s="9"/>
+      <c r="F215" s="9"/>
+      <c r="G215" s="9"/>
+      <c r="H215" s="9"/>
+      <c r="I215" s="9"/>
+      <c r="J215" s="9"/>
+      <c r="K215" s="9"/>
+      <c r="M215" s="9"/>
+      <c r="N215" s="9"/>
+      <c r="O215" s="9"/>
+      <c r="P215" s="9"/>
+      <c r="Q215" s="9"/>
+      <c r="R215" s="9"/>
+      <c r="S215" s="9"/>
+      <c r="T215" s="9"/>
+      <c r="U215" s="9"/>
+    </row>
+    <row r="216" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B216" s="8"/>
+      <c r="D216" s="9"/>
+      <c r="E216" s="9"/>
+      <c r="F216" s="9"/>
+      <c r="G216" s="9"/>
+      <c r="H216" s="9"/>
+      <c r="I216" s="9"/>
+      <c r="J216" s="9"/>
+      <c r="K216" s="9"/>
+      <c r="M216" s="9"/>
+      <c r="N216" s="9"/>
+      <c r="O216" s="9"/>
+      <c r="P216" s="9"/>
+      <c r="Q216" s="9"/>
+      <c r="R216" s="9"/>
+      <c r="S216" s="9"/>
+      <c r="T216" s="9"/>
+      <c r="U216" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
